--- a/docs/enterprise-context/synthetic/apexretail/07-spend-baseline.xlsx
+++ b/docs/enterprise-context/synthetic/apexretail/07-spend-baseline.xlsx
@@ -450,22 +450,22 @@
     <t>SPEND-0-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-01-DATABRICKS</t>
+    <t>SPEND-2026-01-RELEX</t>
   </si>
   <si>
     <t>CC-44090</t>
   </si>
   <si>
-    <t>VEN-DATABRICKS</t>
-  </si>
-  <si>
-    <t>CON-DATABRICKS-2026</t>
-  </si>
-  <si>
-    <t>Retail Analytics</t>
-  </si>
-  <si>
-    <t>SPEND-0-VEN-DATABRICKS</t>
+    <t>VEN-RELEX</t>
+  </si>
+  <si>
+    <t>CON-RELEX-2026</t>
+  </si>
+  <si>
+    <t>Retail Planning Analytics</t>
+  </si>
+  <si>
+    <t>SPEND-0-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-01-SNOW</t>
@@ -564,10 +564,10 @@
     <t>SPEND-1-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-02-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-1-VEN-DATABRICKS</t>
+    <t>SPEND-2026-02-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-1-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-02-SNOW</t>
@@ -642,10 +642,10 @@
     <t>SPEND-2-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-03-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-2-VEN-DATABRICKS</t>
+    <t>SPEND-2026-03-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-2-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-03-SNOW</t>
@@ -720,10 +720,10 @@
     <t>SPEND-3-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-04-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-3-VEN-DATABRICKS</t>
+    <t>SPEND-2026-04-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-3-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-04-SNOW</t>
@@ -795,10 +795,10 @@
     <t>SPEND-4-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-05-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-4-VEN-DATABRICKS</t>
+    <t>SPEND-2026-05-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-4-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-05-SNOW</t>
@@ -873,10 +873,10 @@
     <t>SPEND-5-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-06-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-5-VEN-DATABRICKS</t>
+    <t>SPEND-2026-06-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-5-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-06-SNOW</t>
@@ -951,10 +951,10 @@
     <t>SPEND-6-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-07-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-6-VEN-DATABRICKS</t>
+    <t>SPEND-2026-07-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-6-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-07-SNOW</t>
@@ -1029,10 +1029,10 @@
     <t>SPEND-7-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-08-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-7-VEN-DATABRICKS</t>
+    <t>SPEND-2026-08-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-7-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-08-SNOW</t>
@@ -1107,10 +1107,10 @@
     <t>SPEND-8-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-09-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-8-VEN-DATABRICKS</t>
+    <t>SPEND-2026-09-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-8-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-09-SNOW</t>
@@ -1185,10 +1185,10 @@
     <t>SPEND-9-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-10-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-9-VEN-DATABRICKS</t>
+    <t>SPEND-2026-10-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-9-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-10-SNOW</t>
@@ -1263,10 +1263,10 @@
     <t>SPEND-10-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-11-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-10-VEN-DATABRICKS</t>
+    <t>SPEND-2026-11-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-10-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-11-SNOW</t>
@@ -1341,10 +1341,10 @@
     <t>SPEND-11-VEN-GENESYS</t>
   </si>
   <si>
-    <t>SPEND-2026-12-DATABRICKS</t>
-  </si>
-  <si>
-    <t>SPEND-11-VEN-DATABRICKS</t>
+    <t>SPEND-2026-12-RELEX</t>
+  </si>
+  <si>
+    <t>SPEND-11-VEN-RELEX</t>
   </si>
   <si>
     <t>SPEND-2026-12-SNOW</t>
